--- a/virtual_event_forms/021_webinar_attendance_benchmark_report_request_form--virtual_event_forms.xlsx
+++ b/virtual_event_forms/021_webinar_attendance_benchmark_report_request_form--virtual_event_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -987,8 +987,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'yes',_'value':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Yes', 'value': 'yes'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'no',_'value':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'No', 'value': 'no'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'social_media',_'value':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Social Media', 'value': 'social_media'}</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Email', 'value': 'email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'influencer',_'value':_'influencer'}</t>
+          <t>influencer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Influencer', 'value': 'influencer'}</t>
+          <t>Influencer</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'website',_'value':_'website'}</t>
+          <t>website</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Website', 'value': 'website'}</t>
+          <t>Website</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'blog',_'value':_'blog'}</t>
+          <t>blog</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Blog', 'value': 'blog'}</t>
+          <t>Blog</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'influencer',_'value':_'influencer'}</t>
+          <t>influencer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Influencer', 'value': 'influencer'}</t>
+          <t>Influencer</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'awareness',_'value':_'awareness'}</t>
+          <t>awareness</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Awareness', 'value': 'awareness'}</t>
+          <t>Awareness</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'engagement',_'value':_'engagement'}</t>
+          <t>engagement</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Engagement', 'value': 'engagement'}</t>
+          <t>Engagement</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'conversion',_'value':_'conversion'}</t>
+          <t>conversion</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Conversion', 'value': 'conversion'}</t>
+          <t>Conversion</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'live',_'value':_'live'}</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Live', 'value': 'live'}</t>
+          <t>Live</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'pre-recorded',_'value':_'pre-recorded'}</t>
+          <t>pre-recorded</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Pre-recorded', 'value': 'pre-recorded'}</t>
+          <t>Pre-recorded</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'hybrid',_'value':_'hybrid'}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Hybrid', 'value': 'hybrid'}</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'general_public',_'value':_'general_public'}</t>
+          <t>general_public</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'General public', 'value': 'general_public'}</t>
+          <t>General public</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'specific_industry',_'value':_'specific_industry'}</t>
+          <t>specific_industry</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Specific Industry', 'value': 'specific_industry'}</t>
+          <t>Specific Industry</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'targeted_audience',_'value':_'targeted_audience'}</t>
+          <t>targeted_audience</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Targeted audience', 'value': 'targeted_audience'}</t>
+          <t>Targeted audience</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'webinar',_'value':_'webinar'}</t>
+          <t>webinar</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Webinar', 'value': 'webinar'}</t>
+          <t>Webinar</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'video',_'value':_'video'}</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Video', 'value': 'video'}</t>
+          <t>Video</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'presentation',_'value':_'presentation'}</t>
+          <t>presentation</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Presentation', 'value': 'presentation'}</t>
+          <t>Presentation</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'english',_'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'English', 'value': 'english'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'spanish',_'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Spanish', 'value': 'spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'chinese',_'value':_'chinese'}</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Chinese', 'value': 'chinese'}</t>
+          <t>Chinese</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'online',_'value':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Online', 'value': 'online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'offline',_'value':_'offline'}</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Offline', 'value': 'offline'}</t>
+          <t>Offline</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'hybrid',_'value':_'hybrid'}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Hybrid', 'value': 'hybrid'}</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'upcoming',_'value':_'upcoming'}</t>
+          <t>upcoming</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Upcoming', 'value': 'upcoming'}</t>
+          <t>Upcoming</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'past',_'value':_'past'}</t>
+          <t>past</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Past', 'value': 'past'}</t>
+          <t>Past</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'future',_'value':_'future'}</t>
+          <t>future</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Future', 'value': 'future'}</t>
+          <t>Future</t>
         </is>
       </c>
     </row>
